--- a/src/attributions/attributions_ig_traj_291.xlsx
+++ b/src/attributions/attributions_ig_traj_291.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0736143064681548</v>
+        <v>0.07100224164796258</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2023283625086515</v>
+        <v>0.06840172020421836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005361901149070607</v>
+        <v>-0.03089755993627798</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,79 +1023,79 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005910374655943606</v>
+        <v>-0.006431666657337846</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2017405004068997</v>
+        <v>-0.03716597161819099</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.003175673222564392</v>
+        <v>0.007893419400805025</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0836551046379089</v>
+        <v>0.03498265332121503</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01416007321150566</v>
+        <v>-0.1042889729895999</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03298341659304817</v>
+        <v>0.0348949213430856</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05416417955287071</v>
+        <v>0.02276368287430109</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01788162495550331</v>
+        <v>-0.03171312455897907</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0002069792777307436</v>
+        <v>-0.02004297378725264</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1104,55 +1104,55 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03184932082569965</v>
+        <v>0.1408262992779929</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02827770634814052</v>
+        <v>-0.02746399689094</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06944358562979185</v>
+        <v>0.225579963641463</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1497027310705481</v>
+        <v>0.2527892345612264</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07080831603100772</v>
+        <v>-0.01091005663443047</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.001817919973327277</v>
+        <v>0.03029048940529176</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01418805710578807</v>
+        <v>-0.0544897689327806</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.08649163433815991</v>
+        <v>0.03445411256051222</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03283123518905573</v>
+        <v>-0.07751507694987948</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,58 +1182,58 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03190481457958391</v>
+        <v>-0.07313699072585854</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04257541708426302</v>
+        <v>-0.1041538698950083</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.08905310676590357</v>
+        <v>-0.01285437839436555</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.04640710802875297</v>
+        <v>0.1006499661171699</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01094127294829059</v>
+        <v>-0.1109627508489207</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02004983166574863</v>
+        <v>0.009318476745351634</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,73 +1245,73 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03274941356648393</v>
+        <v>-0.1191100501210888</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03099117283538349</v>
+        <v>-0.03244695650322631</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01593166186343111</v>
+        <v>-0.03308353273716173</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01061381960660221</v>
+        <v>-0.08944428407937945</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02133540246658532</v>
+        <v>0.1183581428301543</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03716094318380431</v>
+        <v>-0.01577864265387069</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04597314766486385</v>
+        <v>-0.1167420196704977</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.03342648399499332</v>
+        <v>-0.02526306251705196</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01017704690408558</v>
+        <v>-0.01238067064964381</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1320,22 +1320,22 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.02874569132567836</v>
+        <v>-0.06965429433188354</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.02900526664094873</v>
+        <v>0.05781790640237333</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03380050877759293</v>
+        <v>-0.005441503209734271</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1344,28 +1344,28 @@
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01950247745448723</v>
+        <v>-0.01823137925905039</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.03637034262361485</v>
+        <v>0.01702264733653246</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01945341551444906</v>
+        <v>0.006859884956712596</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,52 +1377,52 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05668836815106189</v>
+        <v>0.06583487032932205</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.008248668484950638</v>
+        <v>0.1178574993509972</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02434073422596091</v>
+        <v>0.2038074942184618</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04085971144248264</v>
+        <v>-0.09676206328445312</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.06686095049629477</v>
+        <v>0.1779017654498972</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.02407360759003618</v>
+        <v>0.01332005620449062</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04575396385905522</v>
+        <v>-0.06140147501847165</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.0349068518066118</v>
+        <v>0.02506196018271311</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03654119765287879</v>
+        <v>-0.004175484636112474</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,52 +1452,52 @@
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04340351386436194</v>
+        <v>-0.1464308099778442</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.02669773779825179</v>
+        <v>-0.005415940414706789</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01710822948871973</v>
+        <v>-0.0293692916318698</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001691558334483329</v>
+        <v>-0.103888610281098</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.006288705109680439</v>
+        <v>-0.03426679934594072</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.008476023910300627</v>
+        <v>0.07702786658505728</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1506,58 +1506,58 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01406165917757605</v>
+        <v>-0.1398963392539448</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.0184191401413391</v>
+        <v>0.1833510929591033</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.005010644615690384</v>
+        <v>-0.009918671187806824</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03040407898268115</v>
+        <v>-0.05480730763913873</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03399166782388464</v>
+        <v>0.002362178930378545</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,25 +1568,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.02786892888161591</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01359963610322018</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.01975511284127759</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1595,64 +1595,64 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.003253280626950881</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0.0006220044222239862</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.002302617079280415</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.02246715487532366</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.01943618395986903</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.01537357155350929</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.003427457791646328</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1661,94 +1661,94 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.02540764355537866</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.02399778771064515</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.00847547286456485</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.0383175297468698</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.00632481328110616</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.02091698933210228</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.04482217892452542</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.01876096915911531</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01508991213545338</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.02004253941547107</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.009274973126340503</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,88 +1757,88 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.03862102704827943</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.02334300989672726</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.0009192060227398807</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.005215905495389824</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.02913188507934325</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.01033508528605515</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.01982772817955737</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02259632715285675</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.01129406625521932</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.001545857532429557</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.03722072428940856</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.009359625734575995</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.01583966730389294</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.02950110405627189</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.01549452709509967</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.002539817689956104</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1904,49 +1904,49 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.02424979523621847</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.003254440497553733</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0.006309932091480267</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.0229288541966815</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.006840083020336979</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.004047241039780452</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
@@ -1955,52 +1955,52 @@
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.002996759118027361</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.03156482997741717</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.02458193801330648</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.02165803869698094</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.006833474302629623</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.01744508096030569</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.02832743050499036</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.001804092235268539</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.02148469173838996</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,99 +2039,8634 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.03395582919650161</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.01743249239712981</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.03088223254752343</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>-0.01434697050801695</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.002898624875092574</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.00130425495579766</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.01957187960035212</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.01320017332159824</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.01421535624087011</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01643847674151674</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3090452411823946</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06858197226475905</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2580937766420587</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.09468232161605115</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.004537381423014021</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.005321822482219983</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1056316874383861</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.08876752135260182</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1179686885115422</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1204909075576635</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05574707491768357</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1426421313689668</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1240628564336683</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.05468214925075224</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2334080160793761</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6605533326792286</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2446433548197511</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.4145454973390755</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1155903603534005</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.06354345695446442</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1682280474042692</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.07024336343322565</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.08542670307367577</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1569639767492343</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2210686711751446</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.1019873709470566</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.2767261156106648</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2579791212192447</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.06246542476836745</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1771601283681623</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.2419717810089807</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.05823623442732907</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.1487782641373321</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2459956557600103</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.05932614306533676</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1517059269718812</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1304530710247239</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.05258112797751905</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1386717639002207</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.09144986067297706</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.001259247068048539</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.07686626210868473</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1531542436854383</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.04031904439138505</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1717622430373899</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.1246728294020258</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.0876946304949535</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.15251226559154</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1638853005417523</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.1924983131969843</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.1655584447708482</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2373045676457447</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1187707585295715</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1607772201807394</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.1282552618633541</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.06166041973372087</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2840597021542615</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>-0.01354226086905758</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.06358466761025044</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.04977563576019872</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.1201723210806603</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1844128726722734</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.356990222936502</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0220525717311173</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.139113602231268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1384412850576173</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.02962947320802266</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.08891539115063261</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1285754117412413</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1260306164882175</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.03274342816722655</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.0282460201890781</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2331253679905819</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.03407016642560937</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1902961099298199</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1350259023472225</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1387497303333746</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.7401460792974859</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.212844233455272</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.182845444988128</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.02603101642158416</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.06256612241091052</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1058755028573734</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04287204020722209</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.130246068827055</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1469991435735549</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.371863239996362</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.03343428744894922</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2357657079612692</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.2366367439352777</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.02475558903598251</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1593026504163285</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1583482802732657</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.08265434223804126</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.0005368565063359071</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.2141646274406068</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.02103884702721226</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1592680513527125</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.03500064536337061</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.07243342027773597</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0381981839502944</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.1004499681973499</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.005045798389804882</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.01096105966138417</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.08336716842357894</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.07633904146178534</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1252512036742044</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.04290063506293436</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.1298588274190507</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.08025539296084284</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.120314527228706</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.1981833145509987</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.04087401940103448</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.2354908320712711</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.06249427331599514</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1370694691002747</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.2129666420269714</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.07817244621478675</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.224937528140058</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.02923275999523168</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.0009684823460585909</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.0984252938980041</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.08883527549646714</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1032511967407685</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3596587934806102</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04701253394394463</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.1737893151797207</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1972385839958785</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.02050356167385696</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1048566585218731</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1008062043297155</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1309635511870953</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.01664052696451674</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.04464816045266069</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2257415515704195</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.08593729336544681</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1649419863892808</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1102783684175098</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1054153519546961</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.6314944983237311</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1430461270688154</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.1939985228435721</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.00166960569581843</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.05358596249987858</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.1598287888623418</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.03597891687574522</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.07254997340886034</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.04722070850917186</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.308161113444726</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.02883878609189162</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1354880624237273</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.217174321146221</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.04840076487036296</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1321887507124207</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.1295911565612802</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.05421167611691716</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.009374606953762575</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.1940197640021956</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.04769959422431577</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1356734250807938</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.05911762011671604</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.05057888358632381</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.03674997328495205</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.1073022857837814</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.001245428164752054</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.08686405340242774</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.02309928583987801</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1047281624243083</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.1229969291436613</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.05047978054719228</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.1002014461203396</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.04271529679866341</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1020339593147921</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.1000891848899627</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.08794312527388219</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2149313210351812</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.07378981977737391</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1200942846639016</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.2422941632775134</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.06524182636341437</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2489491057001093</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.03214507368865865</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>-0.008439801244018977</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1364030772445146</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.05369989581638961</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.009347113875979477</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5578233739821539</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.002276327687486007</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.06526552827665759</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.2160888884973607</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4993542099199259</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1120233051405439</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.04205129660193223</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.1126920379458048</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1385991341198753</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1466654076126097</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1434895456064261</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.006694252528539393</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1465613418905699</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3394198412530866</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2172587604576743</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.1541780242071397</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2670730249954267</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1450366566588353</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1670010875248334</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1910001426642614</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.8155728531843117</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.004228945384757997</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1414491872986918</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1224664155625487</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.01816792888228675</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.0916837570388969</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.1375731519483069</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.2544931411963827</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.03899142412124584</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.002509924346538094</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1470223782879805</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.009761877696496859</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.3776346301940939</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.086450497649896</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.009874549155010388</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.1655355969374503</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.2702416595451853</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.04023978871117893</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.06583626314199072</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.1165501145961387</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1933365221164951</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.139470317511012</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.01906795409302841</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.08857434423209844</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.2450263319433091</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.04563486735221417</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.08257239161756685</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.1122135875887873</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.048787806640476</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-0.02973966325784675</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.4731048605914669</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.02178720578549196</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.09494536045495842</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.06337540368320493</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.09776319057018079</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.1543843604885614</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.1476123856479851</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.07060383409165563</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.01682263222457325</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.01521958738026408</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.114526649424992</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.07162425893107426</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.1009926891466333</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>-0.02670890678746801</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.09565654023149291</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.08395119485912086</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.07426719753134392</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.2493991858716779</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.2822239029585729</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.0427143634043378</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.1164456146798406</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.08940379044054639</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.2221661969964162</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.1418176003039721</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.03954314121581561</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.3488679216806419</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1847785072457316</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.2851599745447508</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.006130310389735823</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.08912753497891127</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.09927253597834998</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.194549181245576</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.08116691836157176</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2084792159555122</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.006384425030151558</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.189834941200862</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1096166751430972</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.04994366285250167</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1275513823510485</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.07447894772877092</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.01028612858590421</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.03034365880860297</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.04934224178435086</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1325664531607018</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.02895627485620352</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1064408785403294</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.06988470441452106</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1473352732760574</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2712167576070214</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.08545254241921577</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1229258411756775</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08502860584449448</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.1992327461192683</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1106634423137898</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.01639344190314307</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.05520747974159876</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.04510861521099055</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.2043496119656293</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.004108661655667133</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.08431087855857648</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1225254342914704</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.01319583423710121</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.07743273012909681</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0735202445044103</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1443724349365737</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.04107696025664406</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1107408049406598</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.01041636696222213</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.06522510937247344</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.003995657365040254</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.0498187860226145</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.01065246494434375</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.02124188153493036</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.007669797168659903</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.02506587373349488</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.03391614190114071</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.0497579787310474</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.02212487484629061</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.05819865071308115</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.01846939864496878</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.01011193822996479</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.09367782183312537</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.07162776965567434</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.09626699634157608</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1272744353608633</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.003162623344727291</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.06032154245826478</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1259115030178628</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.04267275441389723</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.0993115145385092</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1100794135240663</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.01005489410683047</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.07058023032862215</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.113629337868941</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.03830205089082456</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5148325973131788</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0002700440850149603</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.280564342159551</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6075606347199339</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.1269468041886106</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1982353532227623</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1139995950450614</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.004443227824983744</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1177768790472474</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.03215875159809943</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.06130712917934466</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.07795744972795222</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1657124953135528</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.06451357517745945</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.09482639186049169</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.7338388647635505</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2759153201846885</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.3212020212138874</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1839698045602423</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.01335580953829206</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.0419011910793562</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.009174731277238977</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.089843474575002</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.04391066948069087</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4384048668309342</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.03677873754959628</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1703999915772176</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2394700460300695</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.017515858575498</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1075699391986752</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.09829052415643967</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.07772980135248647</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.04492254828031166</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2237061299253223</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.01441453771117305</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1233328294515248</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.01108555135666103</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.02229123519137749</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.09452965097261611</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.08465824679981289</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.0183323931389147</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.08594244480854549</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1572603468630954</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.06259317427101001</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.1024368562931136</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.1283539480535044</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.05031721999726278</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.0412747467355729</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.0938704795640192</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.0142643575323563</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.04128950148844369</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2578804784633106</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.007625591026963668</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1250087453308819</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1260089855804763</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.01451814246354441</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1362518640586858</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.2368096317537156</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.06122378289717301</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.0101744704646738</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1134967812113027</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.07198302679113594</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.3737637328004914</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1326478602353585</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.07984689236739811</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.4559974253514154</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.223032096262105</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1539367503506809</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.0402388324492669</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01267256161566748</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.005544661424828436</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.01986218768638529</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1338706937573633</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2222037577602377</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1467362683141169</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.03771858075953894</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.2313778420852493</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2428530737293749</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.140834232216819</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02256290232743481</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.05066757266978159</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.01267303549555298</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.131204742198662</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1121550478169164</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.08290456634644046</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.001854649371135884</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.1967383025962886</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.06910249671461589</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.0085159241749709</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1941410410625169</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.05770707510185234</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.004755495526076575</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.089814116304601</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.08566313376769037</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.03688885645439984</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.203680935099142</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.05883352196937213</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.03258943965871855</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1516227042501961</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.02342471104732869</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.000970404644517681</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.09032915425264003</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.04203099856430466</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.02707078849941816</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.04218837314236253</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.04949671606083903</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.006867971764129158</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2267285513372236</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.0568662035802833</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.03789969876844101</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1168263580159574</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.01012929929656321</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.004782772460820705</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.2302553806432373</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.0707934113191805</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.0006280483128592738</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.08428186888562736</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.1085450814762721</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.03676015370198812</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.1785516605937419</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.01260390136827294</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.05637390529607172</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.2022148667834</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.001531745628289719</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3451182324101872</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.02415007276200525</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1423975481477552</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4556398729406052</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1057542333602102</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2037387679502438</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.0994621737550056</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1181451646230026</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.01165391202914747</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.03181093238320283</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2802260515972894</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.0004806981102348303</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.03391320067782991</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.04382687751844315</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.01800998439388342</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.490930550772916</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2412630341333792</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1060183635823349</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.03244371999040717</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.01743696709524062</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.08854328880803962</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.0555858806580355</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.08095184223925117</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.0353695774531211</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.2645884054932645</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.07607225122038919</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.1065766498934343</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1128628071677499</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.02940671068759908</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.05005876308788209</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1176648399683078</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.0987659328249483</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.09696302121904032</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1132667735478171</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.008266387471978583</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.07134993351079165</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.04182103570936625</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1773522024170269</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.05430905562071246</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.006789881564130029</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.06165173203514228</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.07945600496514979</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.0203989119697206</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.0676568575607339</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.03633715307927934</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.04598912915854268</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.02204225341916105</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.009853383573066175</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.005227696832770167</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.01220162516658875</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1364584260180013</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.130932432158351</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.002061555924192711</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.03987951912620769</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.2075057372435904</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.08888362194263089</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1169911234280748</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.01095474566180105</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.02433236845990461</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.04959525460895942</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.0392241248176862</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.06229019800014492</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3740873085411197</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.01212069175337799</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1420221622722794</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4550155857997566</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.1030346101625517</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.1872297503630286</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.08850790259557874</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.08737791763617689</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.01195679459117023</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.03445648712941773</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.2456376296061947</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.01208147322881906</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.03864887039576933</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.03478953138166604</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.004348853773135694</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.4082565567656767</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.2569226983256364</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.1019174011449789</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.007966828915457077</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.003299825105484479</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.06672767056896817</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.03790515352353375</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.05412149956945281</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.02904912448350688</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.2284431608214726</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.06484531704446789</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.108101791999787</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.106248834828522</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.02637823890535754</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.05235108424751526</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.1167963372686887</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.1418910920064637</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.06948314519810558</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.1042914444843911</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.01336787605902164</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.07393732256271993</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0.07613463879940778</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.2088158290936235</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.0664830782668345</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.01453139399809695</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0.04380413370108927</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.04598420032442908</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0.008128724834928856</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.05739258479727879</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.02186635189298738</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0.04910027289638845</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.009966225733988959</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>-0.0008290111176221996</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.03263751016830274</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.01666909488296208</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0.1081606505080878</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.1236182570442468</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.001119420975175839</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.04480882699908054</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.1682489665630392</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.08182097191585727</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0.1168730928665216</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.001766033095943371</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0.008890543018079875</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>-0.02826654740530361</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.03526500023485375</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.06675703004937075</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.2568294364946774</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.08360029537802897</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.1124021230301778</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2217196001047798</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.007165351043765546</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.1079803910484537</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.06928175277144705</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.04621480493013201</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.08056909819103956</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.0545615304003013</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.03953367418522752</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.05219803461472458</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.01635961694893267</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.0310684134670413</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.01725490832228489</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.0180578642833223</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.08887558904301493</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.007113253437926324</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.1617831854512066</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.02019540684000256</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.002295561210419389</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.06679451029213296</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1113391538630767</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.03653506681344443</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.02642080760106553</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-0.0702652693062062</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-0.1104025499013803</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0.06422544393623388</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.007021126430780321</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.03115380220022167</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.01181028276288585</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0.08373939567032432</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-0.04380478783386278</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0.06726026660128644</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0.004563328884568592</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0.03598994833441783</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0.005146031250466448</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>-0.06032322361351384</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0.01431398112090277</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0.03987372890085466</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>-0.05332094162376333</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0.08169112504517606</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0.02465871043844876</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.1237911810008313</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0.06352424167544639</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0.003466002153019663</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.02625681375732344</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0.0510532135942809</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>-0.03844273207820576</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0.006067814825159359</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>0.04406886628997701</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>-0.05967497713790787</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.006747037493913817</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0.04533085295682484</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>0.127769368547643</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-5.861337664423544e-05</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0.1059281336776556</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0.003074093359563177</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.001590208613466223</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0.04096364891334509</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>0.0725763631748053</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0.07896609230274053</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG18" t="n">
         <v>0</v>
       </c>
     </row>
